--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +429,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id_propietario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>nombre_propietario</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nombre_entrenador</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,318 +463,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>LEGACY_ARSENATI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Arsenati</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>ARS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Arsenati</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Histórico</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>SYS_COMPUTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>MER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Futmondo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5f45324dec331549297ee971</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jatafe club de gafe</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JAT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Jatafe</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Trujillo</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5f453062ec331549297ee6b8</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Real Dendryd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Deninho</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5f4530beec331549297ee6d6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>URS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>URSS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Raulético de Madroto</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cruyffisme FC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CRU</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Cruyffisme FC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Mister Seijames</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5f4531e9764e7d491e029746</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cracklos F.C</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CRA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Cracklos F.C</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Solrac24</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bichos  team</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bichos Team</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bichos FC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LEGACY_ARSENATI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Arsenati</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Arsenati</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Desconocido</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Histórico</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SYS_COMPUTER</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mercado Libre</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Mercado</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Futmondo</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>Sistema</t>
         </is>

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,62 +463,318 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LEGACY_ARSENATI</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arsenati</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Arsenati</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Histórico</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Real Dendryd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Deninho</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Unión Raulética de Santanguissa URSS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>URS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>URSS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Raulético de Madroto</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cracklos F.C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CRA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cracklos F.C</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Solrac24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jatafe club de gafe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JAT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jatafe</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Trujillo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bichos  team</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bichos Team</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bichos FC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cruyffisme FC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CRU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cruyffisme FC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mister Seijames</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pallejandro S.A.D</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pallejandro</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Alejandro Lotina</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LEGACY_ARSENATI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arsenati</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Arsenati</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Desconocido</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SYS_COMPUTER</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Mercado Libre</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>MER</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Mercado</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Futmondo</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Sistema</t>
         </is>

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>FC Mikelona⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Mikelona⭐️⭐️⭐️</t>
+          <t>FC Mikelona 🐐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>FC Mikelona 🐐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Mikelona 🐐</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
